--- a/sample-data/goc-ho-coffee/03_du_lieu_ban_hang_3_thang.xlsx
+++ b/sample-data/goc-ho-coffee/03_du_lieu_ban_hang_3_thang.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="R5e20057fce744c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Giao dịch" sheetId="2" r:id="Rf6155825c8834041"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu" sheetId="3" r:id="R91c53000b8934191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="R699b38fdad714f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Giao dịch" sheetId="2" r:id="R366d98576aca411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu" sheetId="3" r:id="Rfc13f1e77490474a"/>
   </x:sheets>
 </x:workbook>
 </file>
